--- a/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -228,12 +228,28 @@
   </si>
   <si>
     <t>战士</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>BallPlayer</t>
+  </si>
+  <si>
+    <t>球球玩家</t>
+  </si>
+  <si>
+    <t>BallFood</t>
+  </si>
+  <si>
+    <t>食物球</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -312,22 +328,22 @@
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -336,21 +352,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -647,28 +663,28 @@
     <col min="15" max="15" width="5.1640625" customWidth="1"/>
     <col min="16" max="16" width="6.1640625" customWidth="1"/>
     <col min="17" max="17" width="5.1640625" customWidth="1"/>
-    <col min="18" max="18" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" bestFit="1" width="3.5" customWidth="1"/>
+    <col min="19" max="19" bestFit="1" width="7" customWidth="1"/>
+    <col min="20" max="20" bestFit="1" width="6.1640625" customWidth="1"/>
+    <col min="21" max="21" bestFit="1" width="5.33203125" customWidth="1"/>
+    <col min="22" max="22" bestFit="1" width="4.1640625" customWidth="1"/>
+    <col min="23" max="23" bestFit="1" width="5.33203125" customWidth="1"/>
+    <col min="25" max="25" bestFit="1" width="5.33203125" customWidth="1"/>
+    <col min="26" max="26" bestFit="1" width="4.5" customWidth="1"/>
+    <col min="27" max="28" bestFit="1" width="5.33203125" customWidth="1"/>
+    <col min="29" max="29" bestFit="1" width="2.83203125" customWidth="1"/>
+    <col min="30" max="30" bestFit="1" width="5.33203125" customWidth="1"/>
+    <col min="31" max="31" bestFit="1" width="2.83203125" customWidth="1"/>
+    <col min="32" max="32" bestFit="1" width="5.33203125" customWidth="1"/>
+    <col min="33" max="33" bestFit="1" width="6.1640625" customWidth="1"/>
+    <col min="34" max="34" bestFit="1" width="5.33203125" customWidth="1"/>
+    <col min="35" max="35" bestFit="1" width="6.1640625" customWidth="1"/>
+    <col min="36" max="36" bestFit="1" width="5.33203125" customWidth="1"/>
+    <col min="37" max="37" bestFit="1" width="2.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
@@ -720,8 +736,8 @@
       <c r="AJ1" s="10"/>
       <c r="AK1" s="10"/>
     </row>
-    <row r="2" spans="1:37">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -773,8 +789,8 @@
       <c r="AJ2" s="10"/>
       <c r="AK2" s="10"/>
     </row>
-    <row r="3" spans="1:37">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="6"/>
@@ -818,8 +834,8 @@
       <c r="AJ3" s="10"/>
       <c r="AK3" s="10"/>
     </row>
-    <row r="4" spans="1:37">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" s="0" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -901,7 +917,7 @@
       </c>
       <c r="AK4" s="15"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5">
       <c r="B5" s="5">
         <v>1001</v>
       </c>
@@ -1011,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6">
       <c r="B6" s="5">
         <v>1002</v>
       </c>
@@ -1105,7 +1121,7 @@
       <c r="AJ6" s="4"/>
       <c r="AK6" s="1"/>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7">
       <c r="B7" s="5">
         <v>1003</v>
       </c>
@@ -1199,7 +1215,7 @@
       <c r="AJ7" s="4"/>
       <c r="AK7" s="1"/>
     </row>
-    <row r="8" spans="1:37">
+    <row r="8">
       <c r="B8" s="5">
         <v>1004</v>
       </c>
@@ -1293,7 +1309,7 @@
       <c r="AJ8" s="4"/>
       <c r="AK8" s="1"/>
     </row>
-    <row r="9" spans="1:37">
+    <row r="9">
       <c r="B9" s="5">
         <v>1005</v>
       </c>
@@ -1383,67 +1399,233 @@
       <c r="AJ9" s="4"/>
       <c r="AK9" s="1"/>
     </row>
-    <row r="10" spans="1:37">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="1"/>
-    </row>
-    <row r="11" spans="1:37">
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="5"/>
-      <c r="AC11" s="1"/>
-    </row>
-    <row r="12" spans="1:37">
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="8">
+        <v>1101</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="3">
+        <v>500</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1780</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>68000</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="U10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG10" s="0">
+        <v>25200</v>
+      </c>
+      <c r="AH10" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI10" s="0">
+        <v>10000</v>
+      </c>
+      <c r="AJ10" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK10" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="8">
+        <v>1102</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="3">
+        <v>200</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="U11" s="3">
+        <v>50</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W11" s="3">
+        <v>50</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK11" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -1473,7 +1655,7 @@
       <c r="AB12" s="5"/>
       <c r="AC12" s="1"/>
     </row>
-    <row r="13" spans="1:37">
+    <row r="13">
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -1503,7 +1685,7 @@
       <c r="AB13" s="5"/>
       <c r="AC13" s="1"/>
     </row>
-    <row r="14" spans="1:37">
+    <row r="14">
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -1533,7 +1715,7 @@
       <c r="AB14" s="5"/>
       <c r="AC14" s="1"/>
     </row>
-    <row r="15" spans="1:37">
+    <row r="15">
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -1563,7 +1745,7 @@
       <c r="AB15" s="5"/>
       <c r="AC15" s="1"/>
     </row>
-    <row r="16" spans="1:37">
+    <row r="16">
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -1593,7 +1775,7 @@
       <c r="AB16" s="5"/>
       <c r="AC16" s="1"/>
     </row>
-    <row r="17" spans="2:29">
+    <row r="17">
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -1623,7 +1805,7 @@
       <c r="AB17" s="5"/>
       <c r="AC17" s="1"/>
     </row>
-    <row r="18" spans="2:29">
+    <row r="18">
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -1653,7 +1835,7 @@
       <c r="AB18" s="5"/>
       <c r="AC18" s="1"/>
     </row>
-    <row r="19" spans="2:29">
+    <row r="19">
       <c r="H19" s="4"/>
       <c r="I19" s="3"/>
       <c r="J19" s="5"/>
@@ -1677,7 +1859,7 @@
       <c r="AB19" s="5"/>
       <c r="AC19" s="1"/>
     </row>
-    <row r="20" spans="2:29">
+    <row r="20">
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
       <c r="J20" s="5"/>
@@ -1701,7 +1883,7 @@
       <c r="AB20" s="5"/>
       <c r="AC20" s="1"/>
     </row>
-    <row r="21" spans="2:29">
+    <row r="21">
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
       <c r="J21" s="5"/>
@@ -1725,7 +1907,7 @@
       <c r="AB21" s="5"/>
       <c r="AC21" s="1"/>
     </row>
-    <row r="22" spans="2:29">
+    <row r="22">
       <c r="H22" s="4"/>
       <c r="I22" s="3"/>
       <c r="J22" s="5"/>
@@ -1749,7 +1931,7 @@
       <c r="AB22" s="5"/>
       <c r="AC22" s="1"/>
     </row>
-    <row r="23" spans="2:29">
+    <row r="23">
       <c r="H23" s="4"/>
       <c r="I23" s="3"/>
       <c r="J23" s="5"/>
@@ -1773,7 +1955,7 @@
       <c r="AB23" s="5"/>
       <c r="AC23" s="1"/>
     </row>
-    <row r="24" spans="2:29">
+    <row r="24">
       <c r="H24" s="4"/>
       <c r="I24" s="3"/>
       <c r="J24" s="5"/>
@@ -1797,7 +1979,7 @@
       <c r="AB24" s="5"/>
       <c r="AC24" s="1"/>
     </row>
-    <row r="25" spans="2:29">
+    <row r="25">
       <c r="H25" s="4"/>
       <c r="I25" s="3"/>
       <c r="J25" s="5"/>
@@ -1821,7 +2003,7 @@
       <c r="AB25" s="5"/>
       <c r="AC25" s="1"/>
     </row>
-    <row r="26" spans="2:29">
+    <row r="26">
       <c r="H26" s="4"/>
       <c r="I26" s="3"/>
       <c r="J26" s="5"/>
@@ -1845,7 +2027,7 @@
       <c r="AB26" s="5"/>
       <c r="AC26" s="1"/>
     </row>
-    <row r="27" spans="2:29">
+    <row r="27">
       <c r="H27" s="4"/>
       <c r="I27" s="3"/>
       <c r="J27" s="5"/>
@@ -1870,7 +2052,7 @@
       <c r="AC27" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells>
     <mergeCell ref="Z4:AA4"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="H1:AK1"/>
@@ -1893,5 +2075,11 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>